--- a/data/trans_camb/IQ2601_R2-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IQ2601_R2-Estudios-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-25,6</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-2,95</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3,73</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>-23,05</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-3,97</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>16,77</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-25,6</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-2,95</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,36</t>
+          <t>11,75</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>7,22</t>
+          <t>6,34</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-34,86; -11,0</t>
+          <t>-38,17; -13,78</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-16,55; 9,31</t>
+          <t>-16,71; 10,16</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-11,85; 31,78</t>
+          <t>-22,51; 22,82</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-37,14; -12,89</t>
+          <t>-34,59; -11,61</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-16,04; 9,23</t>
+          <t>-16,21; 9,53</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-26,49; 21,79</t>
+          <t>-16,85; 30,17</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-32,29; -15,44</t>
+          <t>-32,42; -15,66</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-12,52; 5,09</t>
+          <t>-12,1; 5,5</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-10,18; 22,28</t>
+          <t>-11,91; 22,28</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-39,23%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-4,53%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>5,71%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>-33,54%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>-5,78%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>24,4%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-39,23%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-4,53%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>9,46%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-48,16; -17,97</t>
+          <t>-54,13; -22,43</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-22,88; 14,77</t>
+          <t>-23,82; 16,37</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-15,02; 49,89</t>
+          <t>-32,81; 36,35</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-53,87; -22,94</t>
+          <t>-47,92; -18,17</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-22,76; 15,46</t>
+          <t>-22,53; 15,09</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-38,5; 35,04</t>
+          <t>-24,22; 46,37</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-46,01; -24,26</t>
+          <t>-46,41; -24,96</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-17,65; 8,22</t>
+          <t>-17,09; 8,61</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-14,58; 34,54</t>
+          <t>-17,18; 34,28</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-13,97</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1,89</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>8,98</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>-15,45</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>-0,7</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>1,09</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-13,97</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1,89</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>9,27</t>
+          <t>-0,14</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>5,85</t>
+          <t>5,08</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-21,05; -9,66</t>
+          <t>-19,27; -8,84</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,73; 4,59</t>
+          <t>-2,97; 7,07</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,87; 9,81</t>
+          <t>0,89; 16,89</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-19,21; -8,95</t>
+          <t>-20,72; -9,68</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 7,05</t>
+          <t>-5,71; 4,58</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,86; 17,26</t>
+          <t>-9,8; 9,26</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-18,76; -11,07</t>
+          <t>-18,38; -10,94</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,9; 3,98</t>
+          <t>-2,97; 4,39</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 11,32</t>
+          <t>-0,47; 11,17</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-22,09%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2,99%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>14,21%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>-23,52%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>-1,06%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1,66%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-22,09%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>2,99%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>-0,22%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>7,89%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-30,93; -15,15</t>
+          <t>-29,58; -14,47</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-8,39; 7,27</t>
+          <t>-4,45; 11,85</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-11,66; 15,1</t>
+          <t>1,29; 27,31</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-29,47; -14,83</t>
+          <t>-30,52; -15,37</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-4,24; 11,61</t>
+          <t>-8,35; 7,2</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,29; 27,9</t>
+          <t>-14,8; 14,48</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-28,54; -17,6</t>
+          <t>-28,12; -17,45</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-4,4; 6,34</t>
+          <t>-4,49; 7,03</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 18,0</t>
+          <t>-0,71; 17,49</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-18,3</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-8,9</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>6,07</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>-10,05</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-11,37</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-0,91</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-18,3</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-8,9</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,46</t>
+          <t>-1,72</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2,3</t>
+          <t>2,13</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-18,78; -1,6</t>
+          <t>-26,86; -9,42</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-19,97; -3,48</t>
+          <t>-17,0; -0,3</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-13,72; 11,15</t>
+          <t>-9,04; 17,35</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-26,78; -9,85</t>
+          <t>-17,96; -1,19</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-17,26; -0,26</t>
+          <t>-19,35; -2,61</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-9,58; 17,28</t>
+          <t>-13,87; 10,07</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-20,45; -7,75</t>
+          <t>-20,0; -8,35</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-15,46; -4,04</t>
+          <t>-16,04; -3,6</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-7,63; 10,32</t>
+          <t>-7,31; 10,61</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-25,47%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-12,38%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>8,45%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>-13,83%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-15,64%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-1,26%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-25,47%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-12,38%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>-2,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>2,95%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-24,47; -2,37</t>
+          <t>-34,98; -13,38</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-26,79; -5,09</t>
+          <t>-22,53; -0,04</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-18,82; 16,33</t>
+          <t>-12,38; 25,13</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-35,59; -14,52</t>
+          <t>-24,17; -1,78</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-22,53; -0,31</t>
+          <t>-25,73; -3,65</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-13,02; 24,97</t>
+          <t>-18,6; 13,79</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-27,01; -10,87</t>
+          <t>-27,01; -11,72</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-20,72; -5,87</t>
+          <t>-21,4; -5,08</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-10,45; 14,66</t>
+          <t>-9,86; 15,15</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-16,25</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-1,02</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>8,02</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>-15,36</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>-3,8</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>1,82</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-16,25</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-1,02</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,78</t>
+          <t>0,2</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>5,1</t>
+          <t>4,49</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-19,68; -11,26</t>
+          <t>-20,95; -11,97</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-8,12; 0,15</t>
+          <t>-5,21; 3,3</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,46; 8,7</t>
+          <t>1,43; 14,64</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-20,6; -12,12</t>
+          <t>-19,6; -11,53</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,13; 3,01</t>
+          <t>-8,2; 0,21</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,91; 14,08</t>
+          <t>-6,94; 7,14</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-18,8; -12,53</t>
+          <t>-18,71; -12,84</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-5,1; 0,98</t>
+          <t>-5,07; 0,56</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 9,46</t>
+          <t>-0,34; 9,7</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-24,87%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-1,56%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>12,28%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>-22,63%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>-5,6%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>2,68%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-24,87%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-1,56%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>6,74%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-28,44; -16,81</t>
+          <t>-31,04; -19,0</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-11,63; 0,22</t>
+          <t>-7,68; 5,2</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-7,91; 12,95</t>
+          <t>2,19; 23,1</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-30,39; -18,8</t>
+          <t>-28,01; -17,36</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-7,65; 4,81</t>
+          <t>-11,64; 0,32</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,4; 22,22</t>
+          <t>-10,14; 10,71</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-27,58; -19,04</t>
+          <t>-27,64; -19,54</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-7,55; 1,53</t>
+          <t>-7,45; 0,85</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 14,31</t>
+          <t>-0,57; 14,66</t>
         </is>
       </c>
     </row>
